--- a/datasets/day1_excel_foundations/06_sorting_filtering_organizing/practice_completed.xlsx
+++ b/datasets/day1_excel_foundations/06_sorting_filtering_organizing/practice_completed.xlsx
@@ -469,8 +469,8 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -530,12 +530,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
